--- a/document/chapter/excel/Part4_專案時程與組織分工.xlsx
+++ b/document/chapter/excel/Part4_專案時程與組織分工.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\main\document\chapter\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DF55AD-51D8-45D2-B719-308977D77030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435AD0BD-3CF7-41F1-ADCE-9A789C074F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D409C9E1-8754-4380-8DEB-21ABCF0BBDE7}"/>
   </bookViews>
   <sheets>
-    <sheet name="4-1專案排程-甘特圖" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="4-1專案排程-甘特圖-new" sheetId="3" r:id="rId1"/>
+    <sheet name="4-1專案排程-甘特圖" sheetId="1" r:id="rId2"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t>項目</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,6 +183,54 @@
   </si>
   <si>
     <t>預計進度(初評)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>實際進度(初評)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>實際進度(複評)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>預計進度(複評)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>間隔天數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持續天數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>競賽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>實際間隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>實際天數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>實際間隔天數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>競賽參與-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>競賽參與-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型訓練</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -368,7 +420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -513,6 +565,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -551,6 +606,2314 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>項目</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$C$3:$C$36</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45726</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45786</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45765</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>45797</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>45870</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>預計排程</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$E$3:$E$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>93</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>實際進度</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$J$3:$J$36</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="1">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45786</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>45765</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>45797</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>45870</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>實際排程</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F19B61"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$L$3:$L$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="1">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>間隔天數</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$F$3:$F$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="22">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>130</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>再次進行</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$I$3:$I$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="22">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>間隔天數-實際</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$M$3:$M$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>130</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>再次進行-實際</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$P$3:$P$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="120"/>
+        <c:overlap val="100"/>
+        <c:axId val="1066546607"/>
+        <c:axId val="1066545775"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1066546607"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200"/>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1066545775"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1066545775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46000"/>
+          <c:min val="45597"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d;@" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200"/>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1066546607"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="31"/>
+        <c:minorUnit val="25"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200"/>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="12700">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="標楷體" panose="03000509000000000000" pitchFamily="65" charset="-120"/>
+          <a:ea typeface="標楷體" panose="03000509000000000000" pitchFamily="65" charset="-120"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3914260717410324E-2"/>
+          <c:y val="0.18157407407407408"/>
+          <c:w val="0.89653018372703408"/>
+          <c:h val="0.71565616797900267"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$W$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C074-4635-8FCF-FD9E7C419B0E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$X$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>87</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C074-4635-8FCF-FD9E7C419B0E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$Y$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-45839</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-C074-4635-8FCF-FD9E7C419B0E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$Z$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>93</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-C074-4635-8FCF-FD9E7C419B0E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="863862543"/>
+        <c:axId val="863862959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="863862543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="863862959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="863862959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="863862543"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AC$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>間隔天數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AB$2:$AB$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AC$2:$AC$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45726</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45786</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45765</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>45765</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>45797</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>45797</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8CDF-478C-AB2F-86BE45BFBEAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AD$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>持續天數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AB$2:$AB$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AD$2:$AD$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8CDF-478C-AB2F-86BE45BFBEAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AG$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>間隔天數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AB$2:$AB$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AG$2:$AG$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="23">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>130</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8CDF-478C-AB2F-86BE45BFBEAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AH$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>持續天數</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AB$2:$AB$31</c:f>
+              <c:strCache>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$AH$2:$AH$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8CDF-478C-AB2F-86BE45BFBEAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="508381663"/>
+        <c:axId val="508390815"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="508381663"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="508390815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="508390815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="45980"/>
+          <c:min val="45597"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="508381663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="31"/>
+        <c:minorUnit val="25"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -1162,7 +3525,1212 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>809546</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>55418</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>166254</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FEF0212-3585-4BD9-B33E-10D1F6D058D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>196073</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>41565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>633997</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="圖表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{305E375F-21BB-454F-8ADD-F7D2E5C91CB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>424542</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="圖表 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BDAC86E-B27B-4489-9C31-114F71B64735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1499,6 +5067,1232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4F5B69-7053-4CFE-9E8F-903D6D79EF3B}">
+  <dimension ref="A1:AI36"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="5.109375" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="11.21875" customWidth="1"/>
+    <col min="33" max="34" width="11.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C1" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="W1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" s="47">
+        <v>0</v>
+      </c>
+      <c r="X2" s="47">
+        <v>87</v>
+      </c>
+      <c r="Y2" s="47">
+        <f>G35-C33</f>
+        <v>-45839</v>
+      </c>
+      <c r="Z2" s="47">
+        <v>93</v>
+      </c>
+      <c r="AB2" t="str">
+        <f>A3</f>
+        <v>技術學習</v>
+      </c>
+      <c r="AC2">
+        <f>C3-B3+45597</f>
+        <v>45597</v>
+      </c>
+      <c r="AD2">
+        <f>272</f>
+        <v>272</v>
+      </c>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C3" s="33">
+        <v>45597</v>
+      </c>
+      <c r="D3" s="33">
+        <v>45868</v>
+      </c>
+      <c r="E3">
+        <f>D3-C3+1</f>
+        <v>272</v>
+      </c>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="AE3">
+        <f>J4-B3+45597</f>
+        <v>45597</v>
+      </c>
+      <c r="AF3">
+        <f>L4</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="J4" s="33">
+        <v>45597</v>
+      </c>
+      <c r="K4" s="33">
+        <v>45868</v>
+      </c>
+      <c r="L4">
+        <f>K4-J4+1</f>
+        <v>272</v>
+      </c>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="AB4" t="str">
+        <f>A5</f>
+        <v>題目發想</v>
+      </c>
+      <c r="AC4">
+        <f>C5-B5+45597</f>
+        <v>45597</v>
+      </c>
+      <c r="AD4">
+        <f>120</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C5" s="33">
+        <v>45597</v>
+      </c>
+      <c r="D5" s="33">
+        <v>45716</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E31" si="0">D5-C5+1</f>
+        <v>120</v>
+      </c>
+      <c r="AC5">
+        <f>J6-B5+45597</f>
+        <v>45597</v>
+      </c>
+      <c r="AD5">
+        <f>L6</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="J6" s="33">
+        <v>45597</v>
+      </c>
+      <c r="K6" s="33">
+        <v>45657</v>
+      </c>
+      <c r="L6">
+        <f>K6-J6+1</f>
+        <v>61</v>
+      </c>
+      <c r="AB6" t="str">
+        <f>A7</f>
+        <v>功能分析</v>
+      </c>
+      <c r="AC6">
+        <f>C7-B7+45597</f>
+        <v>45658</v>
+      </c>
+      <c r="AD6">
+        <f>91</f>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C7" s="38">
+        <v>45658</v>
+      </c>
+      <c r="D7" s="46">
+        <v>45748</v>
+      </c>
+      <c r="E7" s="39">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="2"/>
+      <c r="AC7">
+        <f>J8-B7+45597</f>
+        <v>45658</v>
+      </c>
+      <c r="AD7">
+        <f>L8</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="40">
+        <v>45658</v>
+      </c>
+      <c r="K8" s="40">
+        <v>45717</v>
+      </c>
+      <c r="L8" s="5">
+        <f>K8-J8+1</f>
+        <v>60</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="AB8" t="str">
+        <f>A9</f>
+        <v>系統需求分析</v>
+      </c>
+      <c r="AC8">
+        <f>C9-B9+45597</f>
+        <v>45708</v>
+      </c>
+      <c r="AD8">
+        <f>55</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A9" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C9" s="42">
+        <v>45708</v>
+      </c>
+      <c r="D9" s="45">
+        <v>45762</v>
+      </c>
+      <c r="E9" s="43">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="2"/>
+      <c r="AC9">
+        <f>J10-B9+45597</f>
+        <v>45708</v>
+      </c>
+      <c r="AD9">
+        <f>L10</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="44">
+        <v>45708</v>
+      </c>
+      <c r="K10" s="44">
+        <v>45748</v>
+      </c>
+      <c r="L10" s="21">
+        <f>K10-J10+1</f>
+        <v>41</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="AB10" t="str">
+        <f>A11</f>
+        <v>UI/UX設計</v>
+      </c>
+      <c r="AC10">
+        <f>C11-B11+45597</f>
+        <v>45726</v>
+      </c>
+      <c r="AD10">
+        <f>144</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A11" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C11" s="36">
+        <v>45726</v>
+      </c>
+      <c r="D11" s="36">
+        <v>45869</v>
+      </c>
+      <c r="E11" s="35">
+        <f>D11-C11+1</f>
+        <v>144</v>
+      </c>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="AC11">
+        <f>J12-B11+45597</f>
+        <v>45717</v>
+      </c>
+      <c r="AD11">
+        <f>L12</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="J12" s="33">
+        <v>45717</v>
+      </c>
+      <c r="K12" s="33">
+        <v>45901</v>
+      </c>
+      <c r="L12">
+        <f>K12-J12+1</f>
+        <v>185</v>
+      </c>
+      <c r="AB12" t="str">
+        <f>A15</f>
+        <v>資料庫建置</v>
+      </c>
+      <c r="AC12">
+        <f>C15-B15+45597</f>
+        <v>45730</v>
+      </c>
+      <c r="AD12">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C13" s="33">
+        <v>45687</v>
+      </c>
+      <c r="D13" s="33">
+        <v>45900</v>
+      </c>
+      <c r="E13">
+        <f>D13-C13</f>
+        <v>213</v>
+      </c>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="J14" s="33">
+        <v>45687</v>
+      </c>
+      <c r="K14" s="33">
+        <v>45909</v>
+      </c>
+      <c r="L14">
+        <f>K14-J14</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C15" s="33">
+        <v>45730</v>
+      </c>
+      <c r="D15" s="33">
+        <v>45869</v>
+      </c>
+      <c r="E15">
+        <f>D15-C15+1</f>
+        <v>140</v>
+      </c>
+      <c r="AC15">
+        <f>J16-B15+45597</f>
+        <v>45730</v>
+      </c>
+      <c r="AD15">
+        <f>L16</f>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="J16" s="33">
+        <v>45730</v>
+      </c>
+      <c r="K16" s="33">
+        <v>45883</v>
+      </c>
+      <c r="L16">
+        <f>K16-J16+1</f>
+        <v>154</v>
+      </c>
+      <c r="AB16" t="str">
+        <f>A17</f>
+        <v>API設計</v>
+      </c>
+      <c r="AC16">
+        <f>C17-B17+45597</f>
+        <v>45733</v>
+      </c>
+      <c r="AD16">
+        <f>168</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C17" s="33">
+        <v>45733</v>
+      </c>
+      <c r="D17" s="33">
+        <v>45900</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>168</v>
+      </c>
+      <c r="AC17">
+        <f>J18-B17+45597</f>
+        <v>45733</v>
+      </c>
+      <c r="AD17">
+        <f>L18</f>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="J18" s="33">
+        <v>45733</v>
+      </c>
+      <c r="K18" s="33">
+        <v>45870</v>
+      </c>
+      <c r="L18">
+        <f>K18-J18+1</f>
+        <v>138</v>
+      </c>
+      <c r="AB18" t="str">
+        <f>A19</f>
+        <v>前端開發</v>
+      </c>
+      <c r="AC18">
+        <f>C19-B19+45597</f>
+        <v>45733</v>
+      </c>
+      <c r="AD18">
+        <f>168</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A19" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C19" s="36">
+        <v>45733</v>
+      </c>
+      <c r="D19" s="36">
+        <v>45900</v>
+      </c>
+      <c r="E19" s="35">
+        <f>D19-C19+1</f>
+        <v>168</v>
+      </c>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="AC19">
+        <f>J20-B19+45597</f>
+        <v>45733</v>
+      </c>
+      <c r="AD19">
+        <f>L20</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="J20" s="33">
+        <v>45733</v>
+      </c>
+      <c r="K20" s="33">
+        <v>45904</v>
+      </c>
+      <c r="L20">
+        <f>K20-J20+1</f>
+        <v>172</v>
+      </c>
+      <c r="AB20" t="str">
+        <f>A21</f>
+        <v>後端開發</v>
+      </c>
+      <c r="AC20">
+        <f>C21-B21+45597</f>
+        <v>45748</v>
+      </c>
+      <c r="AD20">
+        <f>153</f>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C21" s="33">
+        <v>45748</v>
+      </c>
+      <c r="D21" s="33">
+        <v>45900</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>153</v>
+      </c>
+      <c r="AC21">
+        <f>J22-B21+45597</f>
+        <v>45748</v>
+      </c>
+      <c r="AD21">
+        <f>L22</f>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="J22" s="33">
+        <v>45748</v>
+      </c>
+      <c r="K22" s="33">
+        <v>45904</v>
+      </c>
+      <c r="L22">
+        <f>K22-J22+1</f>
+        <v>157</v>
+      </c>
+      <c r="AB22" t="str">
+        <f>A23</f>
+        <v>伺服器架設</v>
+      </c>
+      <c r="AC22">
+        <f>C23-B23+45597</f>
+        <v>45748</v>
+      </c>
+      <c r="AD22">
+        <f>153</f>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C23" s="33">
+        <v>45748</v>
+      </c>
+      <c r="D23" s="33">
+        <v>45900</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>153</v>
+      </c>
+      <c r="AC23">
+        <f>J24-B23+45597</f>
+        <v>45748</v>
+      </c>
+      <c r="AD23">
+        <f>L24</f>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="J24" s="33">
+        <v>45748</v>
+      </c>
+      <c r="K24" s="33">
+        <v>45904</v>
+      </c>
+      <c r="L24">
+        <f>K24-J24+1</f>
+        <v>157</v>
+      </c>
+      <c r="AB24" t="str">
+        <f>A33</f>
+        <v>競賽參與-1</v>
+      </c>
+      <c r="AC24">
+        <f>C33-B33+45597</f>
+        <v>45839</v>
+      </c>
+      <c r="AD24">
+        <f>87</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C25" s="33">
+        <v>45786</v>
+      </c>
+      <c r="D25" s="33">
+        <v>45802</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="F25">
+        <f>G25-D25</f>
+        <v>103</v>
+      </c>
+      <c r="G25" s="33">
+        <v>45905</v>
+      </c>
+      <c r="H25" s="33">
+        <v>45915</v>
+      </c>
+      <c r="I25">
+        <f t="shared" ref="I25" si="1">H25-G25+1</f>
+        <v>11</v>
+      </c>
+      <c r="AC25">
+        <f>J26-B25+45597</f>
+        <v>45786</v>
+      </c>
+      <c r="AD25">
+        <f>L26</f>
+        <v>17</v>
+      </c>
+      <c r="AG25">
+        <f>N26-K26</f>
+        <v>103</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" ref="AH25" si="2">P26</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="J26" s="33">
+        <v>45786</v>
+      </c>
+      <c r="K26" s="33">
+        <v>45802</v>
+      </c>
+      <c r="L26">
+        <f>K26-J26+1</f>
+        <v>17</v>
+      </c>
+      <c r="M26">
+        <f>N26-K26</f>
+        <v>103</v>
+      </c>
+      <c r="N26" s="33">
+        <v>45905</v>
+      </c>
+      <c r="O26" s="33">
+        <v>45915</v>
+      </c>
+      <c r="P26">
+        <f t="shared" ref="P26" si="3">O26-N26+1</f>
+        <v>11</v>
+      </c>
+      <c r="AB26" t="str">
+        <f>A27</f>
+        <v>系統測試</v>
+      </c>
+      <c r="AC26">
+        <f>C27-B27+45597</f>
+        <v>45802</v>
+      </c>
+      <c r="AD26">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" ref="AG26" si="4">G27-D27</f>
+        <v>108</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" ref="AH26" si="5">I27</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C27" s="33">
+        <v>45802</v>
+      </c>
+      <c r="D27" s="33">
+        <v>45808</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F27">
+        <f t="shared" ref="F27:F31" si="6">G27-D27</f>
+        <v>108</v>
+      </c>
+      <c r="G27" s="33">
+        <v>45916</v>
+      </c>
+      <c r="H27" s="33">
+        <v>45922</v>
+      </c>
+      <c r="I27">
+        <f t="shared" ref="I27:I29" si="7">H27-G27+1</f>
+        <v>7</v>
+      </c>
+      <c r="AC27">
+        <f>J28-B27+45597</f>
+        <v>45802</v>
+      </c>
+      <c r="AD27">
+        <f>I27</f>
+        <v>7</v>
+      </c>
+      <c r="AG27">
+        <f t="shared" ref="AG27" si="8">N28-K28</f>
+        <v>108</v>
+      </c>
+      <c r="AH27">
+        <f t="shared" ref="AH27" si="9">P28</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="J28" s="33">
+        <v>45802</v>
+      </c>
+      <c r="K28" s="33">
+        <v>45808</v>
+      </c>
+      <c r="L28">
+        <f>K28-J28+1</f>
+        <v>7</v>
+      </c>
+      <c r="M28">
+        <f t="shared" ref="M28:M32" si="10">N28-K28</f>
+        <v>108</v>
+      </c>
+      <c r="N28" s="33">
+        <v>45916</v>
+      </c>
+      <c r="O28" s="33">
+        <v>45922</v>
+      </c>
+      <c r="P28">
+        <f t="shared" ref="P28" si="11">O28-N28+1</f>
+        <v>7</v>
+      </c>
+      <c r="AB28" t="str">
+        <f>A29</f>
+        <v>文件製作</v>
+      </c>
+      <c r="AC28">
+        <f>C29-B29+45597</f>
+        <v>45765</v>
+      </c>
+      <c r="AD28">
+        <f>36</f>
+        <v>36</v>
+      </c>
+      <c r="AG28">
+        <f t="shared" ref="AG28" si="12">G29-D29</f>
+        <v>117</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" ref="AH28" si="13">I29</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C29" s="33">
+        <v>45765</v>
+      </c>
+      <c r="D29" s="33">
+        <v>45800</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="6"/>
+        <v>117</v>
+      </c>
+      <c r="G29" s="33">
+        <v>45917</v>
+      </c>
+      <c r="H29" s="33">
+        <v>45933</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="AC29">
+        <f>J30-B29+45597</f>
+        <v>45765</v>
+      </c>
+      <c r="AD29">
+        <f>L30</f>
+        <v>36</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" ref="AG29" si="14">N30-K30</f>
+        <v>117</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" ref="AH29" si="15">P30</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="J30" s="33">
+        <v>45765</v>
+      </c>
+      <c r="K30" s="33">
+        <v>45800</v>
+      </c>
+      <c r="L30">
+        <f>K30-J30+1</f>
+        <v>36</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="10"/>
+        <v>117</v>
+      </c>
+      <c r="N30" s="33">
+        <v>45917</v>
+      </c>
+      <c r="O30" s="33">
+        <v>45933</v>
+      </c>
+      <c r="P30">
+        <f t="shared" ref="P30" si="16">O30-N30+1</f>
+        <v>17</v>
+      </c>
+      <c r="AB30" t="str">
+        <f>A31</f>
+        <v>簡報製作</v>
+      </c>
+      <c r="AC30">
+        <f>C31-B31+45597</f>
+        <v>45797</v>
+      </c>
+      <c r="AD30">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" ref="AG30" si="17">G31-D31</f>
+        <v>130</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" ref="AH30" si="18">I31</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C31" s="33">
+        <v>45797</v>
+      </c>
+      <c r="D31" s="33">
+        <v>45804</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="6"/>
+        <v>130</v>
+      </c>
+      <c r="G31" s="33">
+        <v>45934</v>
+      </c>
+      <c r="H31" s="33">
+        <v>45939</v>
+      </c>
+      <c r="I31">
+        <f t="shared" ref="I31" si="19">H31-G31+1</f>
+        <v>6</v>
+      </c>
+      <c r="AC31">
+        <f>J32-B31+45597</f>
+        <v>45797</v>
+      </c>
+      <c r="AD31">
+        <f>L32</f>
+        <v>8</v>
+      </c>
+      <c r="AG31">
+        <f t="shared" ref="AG31" si="20">N32-K32</f>
+        <v>130</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" ref="AH31" si="21">P32</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="J32" s="33">
+        <v>45797</v>
+      </c>
+      <c r="K32" s="33">
+        <v>45804</v>
+      </c>
+      <c r="L32">
+        <f>K32-J32+1</f>
+        <v>8</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="10"/>
+        <v>130</v>
+      </c>
+      <c r="N32" s="33">
+        <v>45934</v>
+      </c>
+      <c r="O32" s="33">
+        <v>45939</v>
+      </c>
+      <c r="P32">
+        <f t="shared" ref="P32" si="22">O32-N32+1</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C33" s="33">
+        <v>45839</v>
+      </c>
+      <c r="D33" s="33">
+        <v>45925</v>
+      </c>
+      <c r="E33">
+        <f>D33-C33+1</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="J34" s="33">
+        <v>45839</v>
+      </c>
+      <c r="K34" s="33">
+        <v>45925</v>
+      </c>
+      <c r="L34">
+        <f t="shared" ref="L34" si="23">K34-J34+1</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C35" s="33">
+        <v>45870</v>
+      </c>
+      <c r="D35" s="33">
+        <v>45962</v>
+      </c>
+      <c r="E35">
+        <f>D35-C35+1</f>
+        <v>93</v>
+      </c>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="AC35">
+        <f>J34-B33+45597</f>
+        <v>45839</v>
+      </c>
+      <c r="AD35">
+        <f>L34</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="J36" s="33">
+        <v>45870</v>
+      </c>
+      <c r="K36" s="33">
+        <v>45930</v>
+      </c>
+      <c r="L36">
+        <f>K36-J36+1</f>
+        <v>61</v>
+      </c>
+      <c r="AB36" t="str">
+        <f>A25</f>
+        <v>系統整合</v>
+      </c>
+      <c r="AC36">
+        <f>C25-B25+45597</f>
+        <v>45786</v>
+      </c>
+      <c r="AD36">
+        <f>17</f>
+        <v>17</v>
+      </c>
+      <c r="AG36">
+        <f>G25-D25</f>
+        <v>103</v>
+      </c>
+      <c r="AH36">
+        <f>I25</f>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="N1:P1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FA1189-D4CA-41F5-B0C8-9BC8C5907047}">
   <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -1520,19 +6314,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
       <c r="E1" s="34"/>
       <c r="F1" s="34"/>
       <c r="G1" s="34"/>
-      <c r="H1" s="47" t="s">
+      <c r="H1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -2013,7 +6807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA9E0CE5-BC40-4C57-9DD9-345649793A2D}">
   <dimension ref="A1:AW31"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -2061,81 +6855,81 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="48" t="s">
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="48" t="s">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="48" t="s">
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="48" t="s">
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="48" t="s">
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="48" t="s">
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="50"/>
-      <c r="AD1" s="48" t="s">
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="50"/>
-      <c r="AH1" s="48" t="s">
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="48" t="s">
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="AM1" s="49"/>
-      <c r="AN1" s="49"/>
-      <c r="AO1" s="50"/>
-      <c r="AP1" s="48" t="s">
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="AQ1" s="49"/>
-      <c r="AR1" s="49"/>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="48" t="s">
+      <c r="AQ1" s="50"/>
+      <c r="AR1" s="50"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="49"/>
-      <c r="AV1" s="49"/>
-      <c r="AW1" s="50"/>
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="51"/>
     </row>
     <row r="2" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="13"/>
@@ -2188,7 +6982,7 @@
       <c r="AW2" s="17"/>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A3" s="52"/>
+      <c r="A3" s="53"/>
       <c r="B3" s="31"/>
       <c r="C3" s="32"/>
       <c r="D3" s="26"/>
@@ -2239,7 +7033,7 @@
       <c r="AW3" s="21"/>
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="52" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="23"/>
@@ -2292,7 +7086,7 @@
       <c r="AW4" s="17"/>
     </row>
     <row r="5" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A5" s="52"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="18"/>
       <c r="C5" s="32"/>
       <c r="D5" s="26"/>
@@ -2343,7 +7137,7 @@
       <c r="AW5" s="21"/>
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="52" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="23"/>
@@ -2396,7 +7190,7 @@
       <c r="AW6" s="17"/>
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A7" s="52"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="18"/>
       <c r="C7" s="10"/>
       <c r="D7" s="12"/>
@@ -2447,7 +7241,7 @@
       <c r="AW7" s="21"/>
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="52" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="23"/>
@@ -2500,7 +7294,7 @@
       <c r="AW8" s="17"/>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A9" s="52"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="18"/>
       <c r="C9" s="10"/>
       <c r="D9" s="12"/>
@@ -2551,7 +7345,7 @@
       <c r="AW9" s="21"/>
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="52" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="23"/>
@@ -2604,7 +7398,7 @@
       <c r="AW10" s="17"/>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="18"/>
       <c r="C11" s="10"/>
       <c r="D11" s="12"/>
@@ -2655,7 +7449,7 @@
       <c r="AW11" s="21"/>
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="52" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="23"/>
@@ -2708,7 +7502,7 @@
       <c r="AW12" s="17"/>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="18"/>
       <c r="C13" s="10"/>
       <c r="D13" s="12"/>
@@ -2759,7 +7553,7 @@
       <c r="AW13" s="21"/>
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="52" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="23"/>
@@ -2812,7 +7606,7 @@
       <c r="AW14" s="17"/>
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A15" s="52"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="18"/>
       <c r="C15" s="10"/>
       <c r="D15" s="12"/>
@@ -2863,7 +7657,7 @@
       <c r="AW15" s="21"/>
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="52" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="23"/>
@@ -2916,7 +7710,7 @@
       <c r="AW16" s="17"/>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A17" s="52"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="18"/>
       <c r="C17" s="10"/>
       <c r="D17" s="12"/>
@@ -2967,7 +7761,7 @@
       <c r="AW17" s="21"/>
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="52" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="23"/>
@@ -3020,7 +7814,7 @@
       <c r="AW18" s="17"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A19" s="52"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="18"/>
       <c r="C19" s="10"/>
       <c r="D19" s="12"/>
@@ -3071,7 +7865,7 @@
       <c r="AW19" s="21"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="52" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="23"/>
@@ -3124,7 +7918,7 @@
       <c r="AW20" s="17"/>
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A21" s="52"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="18"/>
       <c r="C21" s="10"/>
       <c r="D21" s="12"/>
@@ -3175,7 +7969,7 @@
       <c r="AW21" s="21"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="52" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="23"/>
@@ -3228,7 +8022,7 @@
       <c r="AW22" s="17"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A23" s="52"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="18"/>
       <c r="C23" s="10"/>
       <c r="D23" s="12"/>
@@ -3279,7 +8073,7 @@
       <c r="AW23" s="21"/>
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="52" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="23"/>
@@ -3332,7 +8126,7 @@
       <c r="AW24" s="17"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A25" s="52"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="18"/>
       <c r="C25" s="10"/>
       <c r="D25" s="12"/>
@@ -3383,7 +8177,7 @@
       <c r="AW25" s="21"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="52" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="23"/>
@@ -3436,7 +8230,7 @@
       <c r="AW26" s="17"/>
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A27" s="52"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="18"/>
       <c r="C27" s="10"/>
       <c r="D27" s="12"/>
@@ -3487,7 +8281,7 @@
       <c r="AW27" s="21"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="52" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="23"/>
@@ -3540,7 +8334,7 @@
       <c r="AW28" s="17"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A29" s="52"/>
+      <c r="A29" s="53"/>
       <c r="B29" s="18"/>
       <c r="C29" s="10"/>
       <c r="D29" s="12"/>
@@ -3591,7 +8385,7 @@
       <c r="AW29" s="21"/>
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="23"/>
@@ -3644,7 +8438,7 @@
       <c r="AW30" s="17"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A31" s="52"/>
+      <c r="A31" s="53"/>
       <c r="B31" s="18"/>
       <c r="C31" s="10"/>
       <c r="D31" s="12"/>

--- a/document/chapter/excel/Part4_專案時程與組織分工.xlsx
+++ b/document/chapter/excel/Part4_專案時程與組織分工.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\main\document\chapter\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435AD0BD-3CF7-41F1-ADCE-9A789C074F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18188746-ABD8-42C8-BF5B-01C7B3477209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D409C9E1-8754-4380-8DEB-21ABCF0BBDE7}"/>
   </bookViews>
@@ -1143,7 +1143,7 @@
                   <c:v>154</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>138</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>172</c:v>
@@ -2431,7 +2431,7 @@
                   <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>138</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>168</c:v>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AD17">
         <f>L18</f>
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
@@ -5640,11 +5640,11 @@
         <v>45733</v>
       </c>
       <c r="K18" s="33">
-        <v>45870</v>
+        <v>45884</v>
       </c>
       <c r="L18">
         <f>K18-J18+1</f>
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="AB18" t="str">
         <f>A19</f>

--- a/document/chapter/excel/Part4_專案時程與組織分工.xlsx
+++ b/document/chapter/excel/Part4_專案時程與組織分工.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\main\document\chapter\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18188746-ABD8-42C8-BF5B-01C7B3477209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF65E417-B1B8-4C34-A073-718EE5C3E210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D409C9E1-8754-4380-8DEB-21ABCF0BBDE7}"/>
   </bookViews>
@@ -8490,13 +8490,14 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="AP1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="AL1:AO1"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -8509,14 +8510,13 @@
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="AP1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="AL1:AO1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/document/chapter/excel/Part4_專案時程與組織分工.xlsx
+++ b/document/chapter/excel/Part4_專案時程與組織分工.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\main\document\chapter\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF65E417-B1B8-4C34-A073-718EE5C3E210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4DBE68-7E44-42E7-91FF-EE4A0C485B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D409C9E1-8754-4380-8DEB-21ABCF0BBDE7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
   <si>
     <t>項目</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -231,6 +231,14 @@
   </si>
   <si>
     <t>模型訓練</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>策展籌備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最終文件製作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -638,9 +646,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -687,9 +695,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -697,10 +711,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$C$3:$C$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$C$3:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>45597</c:v>
                 </c:pt>
@@ -747,9 +761,15 @@
                   <c:v>45797</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>45948</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>45960</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>45839</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>45870</c:v>
                 </c:pt>
               </c:numCache>
@@ -778,9 +798,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -827,9 +847,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -837,10 +863,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$E$3:$E$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$E$3:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>272</c:v>
                 </c:pt>
@@ -887,9 +913,15 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>87</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>93</c:v>
                 </c:pt>
               </c:numCache>
@@ -917,9 +949,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -966,9 +998,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -976,10 +1014,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$J$3:$J$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$J$3:$J$40</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="1">
                   <c:v>45597</c:v>
                 </c:pt>
@@ -1026,9 +1064,15 @@
                   <c:v>45797</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>45948</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>45960</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>45839</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>45870</c:v>
                 </c:pt>
               </c:numCache>
@@ -1058,9 +1102,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -1107,9 +1151,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -1117,10 +1167,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$L$3:$L$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$L$3:$L$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="1">
                   <c:v>272</c:v>
                 </c:pt>
@@ -1167,9 +1217,15 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>87</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>61</c:v>
                 </c:pt>
               </c:numCache>
@@ -1193,9 +1249,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -1242,9 +1298,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -1257,10 +1319,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="22">
-                  <c:v>103</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>108</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>117</c:v>
@@ -1294,9 +1356,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -1343,9 +1405,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -1358,10 +1426,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="22">
-                  <c:v>11</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>17</c:v>
@@ -1390,9 +1458,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -1439,9 +1507,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -1454,10 +1528,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="23">
-                  <c:v>103</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>108</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>117</c:v>
@@ -1483,9 +1557,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$36</c:f>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>技術學習</c:v>
                 </c:pt>
@@ -1532,9 +1606,15 @@
                   <c:v>簡報製作</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>競賽參與-1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>競賽參與-2</c:v>
                 </c:pt>
               </c:strCache>
@@ -1547,10 +1627,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="23">
-                  <c:v>11</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>17</c:v>
@@ -1625,7 +1705,7 @@
         <c:axId val="1066545775"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="46000"/>
+          <c:max val="46029"/>
           <c:min val="45597"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -1668,7 +1748,7 @@
         <c:crossAx val="1066546607"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="31"/>
+        <c:majorUnit val="30"/>
         <c:minorUnit val="25"/>
       </c:valAx>
     </c:plotArea>
@@ -2461,7 +2541,7 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>36</c:v>
@@ -2563,13 +2643,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="23">
-                  <c:v>103</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>108</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>108</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>117</c:v>
@@ -2673,13 +2753,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="23">
-                  <c:v>11</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>17</c:v>
@@ -4621,13 +4701,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>809546</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>55418</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>166254</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4695,13 +4775,13 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>424542</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>10885</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5068,7 +5148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4F5B69-7053-4CFE-9E8F-903D6D79EF3B}">
-  <dimension ref="A1:AI36"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
@@ -5198,7 +5278,7 @@
         <v>87</v>
       </c>
       <c r="Y2" s="47">
-        <f>G35-C33</f>
+        <f>G39-C37</f>
         <v>-45839</v>
       </c>
       <c r="Z2" s="47">
@@ -5291,7 +5371,7 @@
         <v>45716</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E31" si="0">D5-C5+1</f>
+        <f t="shared" ref="E5:E35" si="0">D5-C5+1</f>
         <v>120</v>
       </c>
       <c r="AC5">
@@ -5807,11 +5887,11 @@
         <v>157</v>
       </c>
       <c r="AB24" t="str">
-        <f>A33</f>
+        <f>A37</f>
         <v>競賽參與-1</v>
       </c>
       <c r="AC24">
-        <f>C33-B33+45597</f>
+        <f>C37-B37+45597</f>
         <v>45839</v>
       </c>
       <c r="AD24">
@@ -5838,17 +5918,17 @@
       </c>
       <c r="F25">
         <f>G25-D25</f>
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="G25" s="33">
-        <v>45905</v>
+        <v>45884</v>
       </c>
       <c r="H25" s="33">
         <v>45915</v>
       </c>
       <c r="I25">
         <f t="shared" ref="I25" si="1">H25-G25+1</f>
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AC25">
         <f>J26-B25+45597</f>
@@ -5860,11 +5940,11 @@
       </c>
       <c r="AG25">
         <f>N26-K26</f>
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AH25">
         <f t="shared" ref="AH25" si="2">P26</f>
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
@@ -5882,17 +5962,17 @@
       </c>
       <c r="M26">
         <f>N26-K26</f>
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="N26" s="33">
-        <v>45905</v>
+        <v>45884</v>
       </c>
       <c r="O26" s="33">
         <v>45915</v>
       </c>
       <c r="P26">
         <f t="shared" ref="P26" si="3">O26-N26+1</f>
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AB26" t="str">
         <f>A27</f>
@@ -5908,11 +5988,11 @@
       </c>
       <c r="AG26">
         <f t="shared" ref="AG26" si="4">G27-D27</f>
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AH26">
         <f t="shared" ref="AH26" si="5">I27</f>
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
@@ -5934,17 +6014,17 @@
       </c>
       <c r="F27">
         <f t="shared" ref="F27:F31" si="6">G27-D27</f>
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="G27" s="33">
-        <v>45916</v>
+        <v>45889</v>
       </c>
       <c r="H27" s="33">
         <v>45922</v>
       </c>
       <c r="I27">
         <f t="shared" ref="I27:I29" si="7">H27-G27+1</f>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AC27">
         <f>J28-B27+45597</f>
@@ -5952,15 +6032,15 @@
       </c>
       <c r="AD27">
         <f>I27</f>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AG27">
         <f t="shared" ref="AG27" si="8">N28-K28</f>
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AH27">
         <f t="shared" ref="AH27" si="9">P28</f>
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
@@ -5978,17 +6058,17 @@
       </c>
       <c r="M28">
         <f t="shared" ref="M28:M32" si="10">N28-K28</f>
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="N28" s="33">
-        <v>45916</v>
+        <v>45889</v>
       </c>
       <c r="O28" s="33">
         <v>45922</v>
       </c>
       <c r="P28">
         <f t="shared" ref="P28" si="11">O28-N28+1</f>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AB28" t="str">
         <f>A29</f>
@@ -6183,99 +6263,171 @@
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B33" s="33">
         <v>45597</v>
       </c>
       <c r="C33" s="33">
-        <v>45839</v>
+        <v>45948</v>
       </c>
       <c r="D33" s="33">
-        <v>45925</v>
+        <v>45997</v>
       </c>
       <c r="E33">
-        <f>D33-C33+1</f>
-        <v>87</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
       <c r="J34" s="33">
-        <v>45839</v>
+        <v>45948</v>
       </c>
       <c r="K34" s="33">
-        <v>45925</v>
+        <v>45997</v>
       </c>
       <c r="L34">
         <f t="shared" ref="L34" si="23">K34-J34+1</f>
-        <v>87</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B35" s="33">
         <v>45597</v>
       </c>
       <c r="C35" s="33">
-        <v>45870</v>
+        <v>45960</v>
       </c>
       <c r="D35" s="33">
-        <v>45962</v>
+        <v>46017</v>
       </c>
       <c r="E35">
-        <f>D35-C35+1</f>
-        <v>93</v>
-      </c>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
       <c r="J35" s="33"/>
       <c r="K35" s="33"/>
-      <c r="AC35">
-        <f>J34-B33+45597</f>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="J36" s="33">
+        <v>45960</v>
+      </c>
+      <c r="K36" s="33">
+        <v>46017</v>
+      </c>
+      <c r="L36">
+        <f t="shared" ref="L36" si="24">K36-J36+1</f>
+        <v>58</v>
+      </c>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C37" s="33">
         <v>45839</v>
       </c>
-      <c r="AD35">
-        <f>L34</f>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="J36" s="33">
+      <c r="D37" s="33">
+        <v>45953</v>
+      </c>
+      <c r="E37">
+        <f>D37-C37+1</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="J38" s="33">
+        <v>45839</v>
+      </c>
+      <c r="K38" s="33">
+        <v>45953</v>
+      </c>
+      <c r="L38">
+        <f t="shared" ref="L38" si="25">K38-J38+1</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="33">
+        <v>45597</v>
+      </c>
+      <c r="C39" s="33">
         <v>45870</v>
       </c>
-      <c r="K36" s="33">
+      <c r="D39" s="33">
+        <v>45962</v>
+      </c>
+      <c r="E39">
+        <f>D39-C39+1</f>
+        <v>93</v>
+      </c>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="AC39">
+        <f>J38-B37+45597</f>
+        <v>45839</v>
+      </c>
+      <c r="AD39">
+        <f>L38</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="J40" s="33">
+        <v>45870</v>
+      </c>
+      <c r="K40" s="33">
         <v>45930</v>
       </c>
-      <c r="L36">
-        <f>K36-J36+1</f>
+      <c r="L40">
+        <f>K40-J40+1</f>
         <v>61</v>
       </c>
-      <c r="AB36" t="str">
+      <c r="AB40" t="str">
         <f>A25</f>
         <v>系統整合</v>
       </c>
-      <c r="AC36">
+      <c r="AC40">
         <f>C25-B25+45597</f>
         <v>45786</v>
       </c>
-      <c r="AD36">
+      <c r="AD40">
         <f>17</f>
         <v>17</v>
       </c>
-      <c r="AG36">
+      <c r="AG40">
         <f>G25-D25</f>
-        <v>103</v>
-      </c>
-      <c r="AH36">
+        <v>82</v>
+      </c>
+      <c r="AH40">
         <f>I25</f>
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -8490,14 +8642,13 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="AP1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="AL1:AO1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -8510,13 +8661,14 @@
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="AP1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="AL1:AO1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/document/chapter/excel/Part4_專案時程與組織分工.xlsx
+++ b/document/chapter/excel/Part4_專案時程與組織分工.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\main\document\chapter\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4DBE68-7E44-42E7-91FF-EE4A0C485B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3B2F56-6764-4669-8236-3FD2422A5244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D409C9E1-8754-4380-8DEB-21ABCF0BBDE7}"/>
   </bookViews>
@@ -2994,6 +2994,1214 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>項目</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$C$3:$C$40</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="38"/>
+                <c:pt idx="0">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45726</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45786</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45765</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>45797</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>45948</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>45960</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>45870</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>預計排程</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$E$3:$E$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="38"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>213</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>93</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>實際進度</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$J$3:$J$40</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="38"/>
+                <c:pt idx="1">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45730</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45786</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>45765</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>45797</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>45948</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>45960</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>45870</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>實際排程</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F19B61"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$L$3:$L$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="38"/>
+                <c:pt idx="1">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>間隔天數</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$F$3:$F$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="22">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>130</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>再次進行</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$I$3:$I$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="22">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>間隔天數-實際</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$M$3:$M$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="23">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>130</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>再次進行-實際</c:v>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$A$3:$A$40</c:f>
+              <c:strCache>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>技術學習</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>題目發想</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>功能分析</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>系統需求分析</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>UI/UX設計</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>模型訓練</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>資料庫建置</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>API設計</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>前端開發</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>後端開發</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>伺服器架設</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>系統整合</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>系統測試</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>文件製作</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>簡報製作</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>策展籌備</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>最終文件製作</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>競賽參與-1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>競賽參與-2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4-1專案排程-甘特圖-new'!$P$3:$P$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="23">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-AED7-4705-9778-2A4DACE048DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="120"/>
+        <c:overlap val="100"/>
+        <c:axId val="1066546607"/>
+        <c:axId val="1066545775"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1066546607"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000"/>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1066545775"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1066545775"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46029"/>
+          <c:min val="45597"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d;@" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000"/>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1066546607"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="30"/>
+        <c:minorUnit val="25"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000"/>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="12700">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="標楷體" panose="03000509000000000000" pitchFamily="65" charset="-120"/>
+          <a:ea typeface="標楷體" panose="03000509000000000000" pitchFamily="65" charset="-120"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -4807,6 +6015,44 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>695246</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>150668</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="圖表 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E487DBF5-3463-468B-8C0C-B03C333BF546}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
